--- a/output/2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Weinmar Machinery Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Sungai Petani, Kedah</t>
@@ -490,7 +489,6 @@
           <t>016-482 1284</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore hardware/macchinari elencato su directory akaido.com.my (pagina verificata via fetch diretto); nessun sito ufficiale reperito.</t>
@@ -498,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -508,7 +506,6 @@
           <t>Multiquip (Kedah) Sendirian Berhad</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Alor Setar, Kedah</t>
@@ -536,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -546,7 +543,6 @@
           <t>Kian Hock Power Tools Service</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Sungai Petani, Kedah</t>
@@ -562,7 +558,6 @@
           <t>016-416 3162 / 019-442 8866</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Vendita e assistenza power tools, macchinari, generatori, ricambi; indirizzo B-16 Lebuh Fairuz 1, Bakar Arang. Confermata tramite directory business/Foursquare.</t>
@@ -570,7 +565,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +575,6 @@
           <t>Berkat Jaya Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Sungai Petani, Kedah</t>
@@ -608,7 +602,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -618,7 +612,6 @@
           <t>Tenaga Berkat Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Sungai Petani, Kedah</t>
@@ -646,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -656,7 +649,6 @@
           <t>ASL Success Enterprise</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Padang Serai, Kedah</t>
@@ -684,7 +676,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -694,7 +686,6 @@
           <t>LS Sena Enterprise</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Pokok Sena, Kedah</t>
@@ -710,7 +701,6 @@
           <t>016-426 9990 / 04-782 1706</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato su directory akaido.com.my.</t>
@@ -718,7 +708,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -728,7 +718,6 @@
           <t>Shan Hardware Trading</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Kulim, Kedah</t>
@@ -739,8 +728,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Esistenza confermata solo tramite directory akaido.com.my (fetch diretto); nessun contatto telefonico/email reperito in altre fonti indipendenti. Verificare ulteriormente.</t>
@@ -758,7 +745,6 @@
           <t>Yong Hardware Enterprise</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Lunas, Kedah</t>
@@ -786,7 +772,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +782,6 @@
           <t>Syarikat Perniagaan Kean Soon</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Alor Setar (Simpang Empat), Kedah</t>
@@ -812,7 +797,6 @@
           <t>019-452 1133 / 012-565 5865</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Confermato come rivenditore hardware/vernici (dealer MICI Paint). Fonte indipendente riporta anche indirizzo 73 Main Road, Simpang Empat, 06650 Alor Setar, tel 04-7641573.</t>
@@ -820,7 +804,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -830,7 +814,6 @@
           <t>Chip Seng Huat Sdn Bhd</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Changlun / Bukit Kayu Hitam, Kedah</t>
@@ -868,7 +851,6 @@
           <t>Chun Machinery</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Jitra, Kedah</t>
@@ -884,7 +866,6 @@
           <t>017-639 9001</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermato indirizzo No.7A Km 25 Teluk Keluang, Jalan Kodiang, Jitra, Kedah.</t>
@@ -892,7 +873,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -902,7 +883,6 @@
           <t>Zicsano Machinery</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Alor Setar, Kedah</t>
@@ -930,7 +910,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -940,7 +920,6 @@
           <t>OKS Super Trading</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Pulau Langkawi, Kedah</t>
@@ -956,7 +935,6 @@
           <t>012-457 6502</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Confermato (titolare Ooi Keat Seong), indirizzo No.21 Pusat Mas, Lorong Tiram, Mukim Kuah, Langkawi. Trading generico elencato come distributore hardware/power tools su akaido.com.my.</t>
@@ -964,7 +942,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -974,7 +952,6 @@
           <t>EWS Northern Hardware</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Langkawi, Kedah</t>
@@ -990,7 +967,6 @@
           <t>012-481 1966</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Confermato su directory akaido.com.my.</t>
@@ -998,7 +974,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1008,7 +984,6 @@
           <t>Mahsuri Hardware (Langkawi) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Langkawi, Kedah</t>
@@ -1024,7 +999,6 @@
           <t>04-955 5916</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Hardware store incorporato nel 2009 (reg. 0857755A); prodotti principali lucchetti e vernici, oltre a hardware generico.</t>
@@ -1032,7 +1006,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1016,6 @@
           <t>PSM Jaya Enterprise</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Baling, Kedah</t>
@@ -1058,7 +1031,6 @@
           <t>017-405 1035</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Vende hardware, distributore principale vernice Jotun a Baling, vende e ripara macchinari. Fonte alternativa riporta anche tel 04-470 5400 / 017-469 5619, indirizzo No.3 Jalan Ahmad, Baling.</t>
@@ -1066,7 +1038,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1048,6 @@
           <t>HE Machinery and Tools Trading (Alor Setar) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Alor Setar, Kedah</t>
@@ -1104,7 +1075,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1117,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1127,6 @@
           <t>MEH Electrical &amp; Hardware Supplies Sdn Bhd</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Kulim / Sungai Petani / Kuala Ketil / Padang Serai, Kedah (multi-sede)</t>
@@ -1184,7 +1154,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1196,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1238,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1248,6 @@
           <t>Shin Tech Electric Tools</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Alor Setar, Kedah</t>
@@ -1306,7 +1275,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1285,6 @@
           <t>Altra Appliances PLT</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Alor Setar, Kedah</t>
@@ -1344,7 +1312,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1342,6 @@
           <t>04-441 6688 / 04-441 6022</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Hardware store generico (Kawasan Perindustrian Taman Ria); non confermata specializzazione in utensili industriali/macchine utensili - verificare pertinenza esatta al settore.</t>
@@ -1382,7 +1349,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1379,6 @@
           <t>+6012-476 1971</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Fornitore macchinari da costruzione dal 1991 (vendita, noleggio, riparazione), dealer autorizzato DongCheng (power tools); buona coerenza col settore.</t>
@@ -1420,7 +1386,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1428,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
